--- a/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami sort des toilettes. Maman est dans le couloir. Maman dit : on lave les mains. Après les toilettes, Sami va ouvrir l'eau. Il ouvre l'eau. Il prend le savon. Il frotte ses mains. Il rince. Il essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Sami va au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte, il rince, il essuie. Maman dit : savon et eau. Sami sourit. Il va à table.</t>
+          <t>Sami sort des toilettes. Maman est dans le couloir. On lave les mains. Après les toilettes, Sami va ouvrir l'eau. Il ouvre l'eau. Il prend le savon. Il frotte ses mains. Il rince. Il essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Sami va au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte, il rince, il essuie. Savon et eau. Sami sourit. Il va à table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami sort des toilettes. Maman est dans le couloir.
+maman|On lave les mains. Après les toilettes, Sami va ouvrir l'eau. Il ouvre l'eau.
+narrateur|Il prend le savon. Il frotte ses mains. Il rince. Il essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Sami va au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte, il rince, il essuie.
+maman|Savon et eau.
+narrateur|Sami sourit. Il va à table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Sami a lavé. Avant de manger, Sami a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'assoit près de maman. Ses mains sont propres. Il dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Sami sourit. Il va à table.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Sami se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Après les toilettes, Sami a lavé. Avant de manger, Sami a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Sami s'assoit près de maman. Ses mains sont propres. Il dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les mains propres de Sami</t>
+          <t>Le savon de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les carreaux sont froids. Après les toilettes, savon. Avant de manger, savon. Nino va à table.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami sort des toilettes. Maman est dans le couloir. On lave les mains. Après les toilettes, Sami va ouvrir l'eau. Il ouvre l'eau. Il prend le savon. Il frotte ses mains. Il rince. Il essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Sami va au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte, il rince, il essuie. Savon et eau. Sami sourit. Il va à table.</t>
+          <t>Les carreaux du couloir sont froids. Un savon jaune attend. Il sent le citron. Le tuyau fait un petit chant. Ça sent déjà le savon. Une serviette blanche est pliée. Une goutte tremble au robinet. La lumière du couloir est douce. Nino, viens au lavabo. On lave les mains. Tu sens le savon ? Oui, maman. Ça sent le citron. En ce moment, Nino vient. Il vient des toilettes. Après les toilettes, on lave. On ouvre l'eau. Nino ouvre l'eau. L'eau est tiède. Elle coule dans le lavabo. Le savon, maintenant. Nino prend le savon. Il frotte ses mains. Le dos, puis les doigts. Ça sent le citron. Ça mousse. Oui. Savon et eau. Nino rince. L'eau emporte la mousse. Il essuie. La serviette est douce. Les mains sont propres. Bravo, Nino. Tu as fait du bon travail. C'est l'heure de manger. La cuisine sent la soupe. Un bol fume déjà, tout près. Tu as faim ? Oui, maman. Avant de manger, on lave. Nino va au lavabo. Il ouvre l'eau. L'eau chante encore. Il prend le savon. Il frotte. Il rince. Il essuie. La serviette sent le propre. Savon et eau. Savon et eau. Tu as lavé tes mains ? Oui, maman. Bravo. Nino va à table. La chaise est un peu froide. Tu t'assois ? Oui, maman. Nino pose ses mains propres. Elles sentent encore le citron.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami sort des toilettes. Maman est dans le couloir.
-maman|On lave les mains. Après les toilettes, Sami va ouvrir l'eau. Il ouvre l'eau.
-narrateur|Il prend le savon. Il frotte ses mains. Il rince. Il essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Sami va au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte, il rince, il essuie.
+          <t>narrateur|Les carreaux du couloir sont froids.
+narrateur|Un savon jaune attend.
+narrateur|Il sent le citron.
+narrateur|Le tuyau fait un petit chant.
+narrateur|Ça sent déjà le savon.
+narrateur|Une serviette blanche est pliée.
+narrateur|Une goutte tremble au robinet.
+narrateur|La lumière du couloir est douce.
+maman|Nino, viens au lavabo.
+maman|On lave les mains.
+maman|Tu sens le savon ?
+enfant-m|Oui, maman.
+enfant-m|Ça sent le citron.
+narrateur|En ce moment, Nino vient.
+narrateur|Il vient des toilettes.
+maman|Après les toilettes, on lave.
+maman|On ouvre l'eau.
+narrateur|Nino ouvre l'eau.
+narrateur|L'eau est tiède.
+narrateur|Elle coule dans le lavabo.
+maman|Le savon, maintenant.
+narrateur|Nino prend le savon.
+narrateur|Il frotte ses mains.
+narrateur|Le dos, puis les doigts.
+narrateur|Ça sent le citron.
+enfant-m|Ça mousse.
+maman|Oui.
 maman|Savon et eau.
-narrateur|Sami sourit. Il va à table.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nino rince.
+narrateur|L'eau emporte la mousse.
+narrateur|Il essuie.
+narrateur|La serviette est douce.
+narrateur|Les mains sont propres.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|C'est l'heure de manger.
+narrateur|La cuisine sent la soupe.
+narrateur|Un bol fume déjà, tout près.
+maman|Tu as faim ?
+enfant-m|Oui, maman.
+maman|Avant de manger, on lave.
+narrateur|Nino va au lavabo.
+narrateur|Il ouvre l'eau.
+narrateur|L'eau chante encore.
+narrateur|Il prend le savon.
+narrateur|Il frotte.
+narrateur|Il rince.
+narrateur|Il essuie.
+narrateur|La serviette sent le propre.
+maman|Savon et eau.
+enfant-m|Savon et eau.
+maman|Tu as lavé tes mains ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Nino va à table.
+narrateur|La chaise est un peu froide.
+maman|Tu t'assois ?
+enfant-m|Oui, maman.
+narrateur|Nino pose ses mains propres.
+narrateur|Elles sentent encore le citron.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eau_robinet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sami se lave les mains. Avec quoi ?</t>
+          <t>Nino se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sami se lave les mains. Avec quoi ?</t>
+          <t>narrateur|Nino se lave les mains.
+narrateur|Avec quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Sami a lavé. Avant de manger, Sami a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+          <t>Après les toilettes, Nino a lavé. Avant de manger, Nino a lavé. Eau, savon, rincer, essuyer. Tu as pris le savon ? Oui, maman. Le savon. Bravo. Savon et eau. Nino sent encore le citron. Ses mains sont sèches. Avant de manger, on a lavé ? Oui. Savon et eau. La goutte du robinet est partie.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1748,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après les toilettes, Sami a lavé. Avant de manger, Sami a lavé. Ouvrir l'eau, savon, rincer, essuyer.</t>
+          <t>narrateur|Après les toilettes, Nino a lavé.
+narrateur|Avant de manger, Nino a lavé.
+narrateur|Eau, savon, rincer, essuyer.
+maman|Tu as pris le savon ?
+enfant-m|Oui, maman.
+enfant-m|Le savon.
+maman|Bravo.
+maman|Savon et eau.
+narrateur|Nino sent encore le citron.
+narrateur|Ses mains sont sèches.
+maman|Avant de manger, on a lavé ?
+enfant-m|Oui.
+enfant-m|Savon et eau.
+narrateur|La goutte du robinet est partie.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sami s'assoit près de maman. Ses mains sont propres. Il dit merci.</t>
+          <t>Nino s'assoit près de maman. Ses mains sont propres. Tu es assis ? Oui, maman. Bravo. Merci, maman. Merci, Nino. On pose la serviette ? Nino pose la serviette. La soupe fume un peu. La table est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1929,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'assoit près de maman. Ses mains sont propres. Il dit merci.</t>
+          <t>narrateur|Nino s'assoit près de maman.
+narrateur|Ses mains sont propres.
+maman|Tu es assis ?
+enfant-m|Oui, maman.
+maman|Bravo.
+enfant-m|Merci, maman.
+maman|Merci, Nino.
+maman|On pose la serviette ?
+narrateur|Nino pose la serviette.
+narrateur|La soupe fume un peu.
+narrateur|La table est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les mains de Nino sentent le citron. Savon et eau. Oui. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2107,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les mains de Nino sentent le citron.
+enfant-m|Savon et eau.
+maman|Oui.
+maman|Bravo, Nino.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les carreaux du couloir sont froids. Un savon jaune attend. Il sent le citron. Le tuyau fait un petit chant. Ça sent déjà le savon. Une serviette blanche est pliée. Une goutte tremble au robinet. La lumière du couloir est douce. Nino, viens au lavabo. On lave les mains. Tu sens le savon ? Oui, maman. Ça sent le citron. En ce moment, Nino vient. Il vient des toilettes. Après les toilettes, on lave. On ouvre l'eau. Nino ouvre l'eau. L'eau est tiède. Elle coule dans le lavabo. Le savon, maintenant. Nino prend le savon. Il frotte ses mains. Le dos, puis les doigts. Ça sent le citron. Ça mousse. Oui. Savon et eau. Nino rince. L'eau emporte la mousse. Il essuie. La serviette est douce. Les mains sont propres. Bravo, Nino. Tu as fait du bon travail. C'est l'heure de manger. La cuisine sent la soupe. Un bol fume déjà, tout près. Tu as faim ? Oui, maman. Avant de manger, on lave. Nino va au lavabo. Il ouvre l'eau. L'eau chante encore. Il prend le savon. Il frotte. Il rince. Il essuie. La serviette sent le propre. Savon et eau. Savon et eau. Tu as lavé tes mains ? Oui, maman. Bravo. Nino va à table. La chaise est un peu froide. Tu t'assois ? Oui, maman. Nino pose ses mains propres. Elles sentent encore le citron.</t>
+          <t>Les carreaux du couloir sont froids. Un savon jaune attend. Il sent le citron. Le tuyau fait un petit chant. Ça sent déjà le savon. Une serviette blanche est pliée. Une goutte tremble au robinet. La lumière du couloir est douce. Nino, viens au lavabo. On lave les mains. Tu sens le savon ? Oui, maman. Ça sent le citron. En ce moment, Nino vient. Il vient des toilettes. Après les toilettes, on lave. On ouvre l'eau. Nino ouvre l'eau. L'eau est tiède. Elle coule dans le lavabo. Le savon, maintenant. Nino prend le savon. Il frotte ses mains. Le dos, puis les doigts. Ça sent le citron. Ça mousse. Oui. Savon et eau. Nino rince. L'eau emporte la mousse. Il essuie. La serviette est douce. Les mains sont propres. Bravo, Nino. C'est l'heure de manger. La cuisine sent la soupe. Un bol fume déjà, tout près. Tu as faim ? Oui, maman. Avant de manger, on lave. Nino va au lavabo. Il ouvre l'eau. L'eau chante encore. Il prend le savon. Il frotte. Il rince. Il essuie. La serviette sent le propre. Savon et eau. Savon et eau. Tu as lavé tes mains ? Oui, maman. Bravo. Nino va à table. La chaise est un peu froide. Tu t'assois ? Oui, maman. Nino pose ses mains propres. Elles sentent encore le citron.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami sort des toilettes. Maman est dans le couloir. Maman dit : on lave les mains. Après les toilettes, Sami va ouvrir l'eau. Il ouvre l'eau. Il prend le &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;. Il frotte ses mains. Il rince. Il essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Sami va au lavabo. Il ouvre l'eau. Il prend le savon. Il frotte, il rince, il essuie. Maman dit : savon et eau. Sami sourit. Il va à table.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les carreaux du couloir sont froids. Un savon jaune attend. Il sent le citron. Le tuyau fait un petit chant. Ça sent déjà le savon. Une serviette blanche est pliée. Une goutte tremble au robinet. La lumière du couloir est douce. Nino, viens au lavabo. On lave les mains. Tu sens le savon ? Oui, maman. Ça sent le citron. En ce moment, Nino vient. Il vient des toilettes. Après les toilettes, on lave. On ouvre l'eau. Nino ouvre l'eau. L'eau est tiède. Elle coule dans le lavabo. Le savon, maintenant. Nino prend le savon. Il frotte ses mains. Le dos, puis les doigts. Ça sent le citron. Ça mousse. Oui. Savon et eau. Nino rince. L'eau emporte la mousse. Il essuie. La serviette est douce. Les mains sont propres. Bravo, Nino. C'est l'heure de manger. La cuisine sent la soupe. Un bol fume déjà, tout près. Tu as faim ? Oui, maman. Avant de manger, on lave. Nino va au lavabo. Il ouvre l'eau. L'eau chante encore. Il prend le savon. Il frotte. Il rince. Il essuie. La serviette sent le propre. Savon et eau. Savon et eau. Tu as lavé tes mains ? Oui, maman. Bravo. Nino va à table. La chaise est un peu froide. Tu t'assois ? Oui, maman. Nino pose ses mains propres. Elles sentent encore le citron.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 narrateur|La serviette est douce.
 narrateur|Les mains sont propres.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
 narrateur|C'est l'heure de manger.
 narrateur|La cuisine sent la soupe.
 narrateur|Un bol fume déjà, tout près.
@@ -1420,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1578,6 @@
 narrateur|Avec quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1609,7 +1607,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après les toilettes, Sami a lavé. Avant de manger, Sami a lavé. Ouvrir l'eau, &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;, rincer, essuyer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après les toilettes, Nino a lavé. Avant de manger, Nino a lavé. Eau, savon, rincer, essuyer. Tu as pris le savon ? Oui, maman. Le savon. Bravo. Savon et eau. Nino sent encore le citron. Ses mains sont sèches. Avant de manger, on a lavé ? Oui. Savon et eau. La goutte du robinet est partie.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1764,7 +1762,6 @@
 narrateur|La goutte du robinet est partie.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1794,7 +1791,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami s'assoit près de maman. Ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s sont propres. Il dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'assoit près de maman. Ses mains sont propres. Tu es assis ? Oui, maman. Bravo. Merci, maman. Merci, Nino. On pose la serviette ? Nino pose la serviette. La soupe fume un peu. La table est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,7 +1939,6 @@
 narrateur|La table est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les mains de Nino sentent le citron. Savon et eau. Oui. Bravo, Nino. L'histoire est finie.</t>
+          <t>Les mains de Nino sentent le citron. Savon et eau. Oui. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les mains de Nino sentent le citron. Savon et eau. Oui. Bravo, Nino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2110,11 +2106,9 @@
           <t>narrateur|Les mains de Nino sentent le citron.
 enfant-m|Savon et eau.
 maman|Oui.
-maman|Bravo, Nino.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Nino.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, couloir, lavabo, table</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
